--- a/src/test/resources/test-data/Open-EMR-data.xlsx
+++ b/src/test/resources/test-data/Open-EMR-data.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/586327d4bf5d9fec/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{FB21DA50-67EC-472F-BC27-F5367F64C26C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54FA943F-8676-48EE-89CB-181C0EA63440}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{FB21DA50-67EC-472F-BC27-F5367F64C26C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94512411-0D48-4AC6-9DFF-D7ABB69D6A2C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{5394AF86-5979-43FA-9CEB-54412C1C0FAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{5394AF86-5979-43FA-9CEB-54412C1C0FAC}"/>
   </bookViews>
   <sheets>
     <sheet name="validLoginTest" sheetId="1" r:id="rId1"/>
     <sheet name="invalidLoginTest" sheetId="2" r:id="rId2"/>
+    <sheet name="addValidPatientTest" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="28">
   <si>
     <t>pass</t>
   </si>
@@ -80,19 +81,61 @@
   </si>
   <si>
     <t>clinician123</t>
+  </si>
+  <si>
+    <t>Invalid username</t>
+  </si>
+  <si>
+    <t>firstName</t>
+  </si>
+  <si>
+    <t>lastName</t>
+  </si>
+  <si>
+    <t>dob</t>
+  </si>
+  <si>
+    <t>gender</t>
+  </si>
+  <si>
+    <t>dashboardHeader</t>
+  </si>
+  <si>
+    <t>Medical Record Dashboard</t>
+  </si>
+  <si>
+    <t>Jack</t>
+  </si>
+  <si>
+    <t>Nick</t>
+  </si>
+  <si>
+    <t>Male</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -115,11 +158,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -538,7 +584,7 @@
     <col min="1" max="1" width="11.88671875" customWidth="1"/>
     <col min="2" max="2" width="14.5546875" customWidth="1"/>
     <col min="3" max="3" width="10.109375" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -565,8 +611,8 @@
       <c r="C2" s="1">
         <v>18</v>
       </c>
-      <c r="D2" t="s">
-        <v>1</v>
+      <c r="D2" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -579,8 +625,8 @@
       <c r="C3" s="1">
         <v>18</v>
       </c>
-      <c r="D3" t="s">
-        <v>1</v>
+      <c r="D3" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -593,8 +639,8 @@
       <c r="C4" s="1">
         <v>18</v>
       </c>
-      <c r="D4" t="s">
-        <v>1</v>
+      <c r="D4" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -607,8 +653,8 @@
       <c r="C5" s="1">
         <v>18</v>
       </c>
-      <c r="D5" t="s">
-        <v>1</v>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -621,8 +667,8 @@
       <c r="C6" s="1">
         <v>18</v>
       </c>
-      <c r="D6" t="s">
-        <v>1</v>
+      <c r="D6" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -635,11 +681,85 @@
       <c r="C7" s="1">
         <v>18</v>
       </c>
-      <c r="D7" t="s">
-        <v>1</v>
+      <c r="D7" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C12E09FD-C77F-4F20-A29C-8979935337C7}">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="25.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="4">
+        <v>46130</v>
+      </c>
+      <c r="H2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>